--- a/artfynd/A 62355-2022 artfynd.xlsx
+++ b/artfynd/A 62355-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133236983</v>
+        <v>133236975</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448089</v>
+        <v>448125</v>
       </c>
       <c r="R2" t="n">
-        <v>6803668</v>
+        <v>6803620</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133236975</v>
+        <v>133236983</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448125</v>
+        <v>448089</v>
       </c>
       <c r="R3" t="n">
-        <v>6803620</v>
+        <v>6803668</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,38 +894,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133236990</v>
+        <v>133236982</v>
       </c>
       <c r="B4" t="n">
-        <v>57145</v>
+        <v>99130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448080</v>
+        <v>448098</v>
       </c>
       <c r="R4" t="n">
-        <v>6803714</v>
+        <v>6803664</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,37 +1005,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133236982</v>
+        <v>133236990</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448098</v>
+        <v>448080</v>
       </c>
       <c r="R5" t="n">
-        <v>6803664</v>
+        <v>6803714</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1344,49 +1344,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133236987</v>
+        <v>133236967</v>
       </c>
       <c r="B8" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448123</v>
+        <v>447997</v>
       </c>
       <c r="R8" t="n">
-        <v>6803736</v>
+        <v>6803635</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1414,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1424,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,45 +1451,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133236967</v>
+        <v>133236987</v>
       </c>
       <c r="B9" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447997</v>
+        <v>448123</v>
       </c>
       <c r="R9" t="n">
-        <v>6803635</v>
+        <v>6803736</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1883,50 +1883,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133236969</v>
+        <v>133236978</v>
       </c>
       <c r="B13" t="n">
-        <v>57145</v>
+        <v>81318</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448047</v>
+        <v>448126</v>
       </c>
       <c r="R13" t="n">
-        <v>6803686</v>
+        <v>6803611</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,7 +1953,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1968,7 +1963,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1995,45 +1990,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133236978</v>
+        <v>133236969</v>
       </c>
       <c r="B14" t="n">
-        <v>81318</v>
+        <v>57145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448126</v>
+        <v>448047</v>
       </c>
       <c r="R14" t="n">
-        <v>6803611</v>
+        <v>6803686</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 62355-2022 artfynd.xlsx
+++ b/artfynd/A 62355-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133236975</v>
+        <v>133236983</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448125</v>
+        <v>448089</v>
       </c>
       <c r="R2" t="n">
-        <v>6803620</v>
+        <v>6803668</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133236983</v>
+        <v>133236975</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448089</v>
+        <v>448125</v>
       </c>
       <c r="R3" t="n">
-        <v>6803668</v>
+        <v>6803620</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,37 +894,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133236982</v>
+        <v>133236990</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448098</v>
+        <v>448080</v>
       </c>
       <c r="R4" t="n">
-        <v>6803664</v>
+        <v>6803714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,38 +1006,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133236990</v>
+        <v>133236982</v>
       </c>
       <c r="B5" t="n">
-        <v>57145</v>
+        <v>99130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448080</v>
+        <v>448098</v>
       </c>
       <c r="R5" t="n">
-        <v>6803714</v>
+        <v>6803664</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1344,45 +1344,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133236967</v>
+        <v>133236987</v>
       </c>
       <c r="B8" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447997</v>
+        <v>448123</v>
       </c>
       <c r="R8" t="n">
-        <v>6803635</v>
+        <v>6803736</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,49 +1455,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133236987</v>
+        <v>133236967</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448123</v>
+        <v>447997</v>
       </c>
       <c r="R9" t="n">
-        <v>6803736</v>
+        <v>6803635</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 62355-2022 artfynd.xlsx
+++ b/artfynd/A 62355-2022 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133236983</v>
+        <v>133236982</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448089</v>
+        <v>448098</v>
       </c>
       <c r="R2" t="n">
-        <v>6803668</v>
+        <v>6803664</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133236975</v>
+        <v>133236983</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448125</v>
+        <v>448089</v>
       </c>
       <c r="R3" t="n">
-        <v>6803620</v>
+        <v>6803668</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1006,37 +1005,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133236982</v>
+        <v>133236975</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448098</v>
+        <v>448125</v>
       </c>
       <c r="R5" t="n">
-        <v>6803664</v>
+        <v>6803620</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1883,45 +1883,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133236978</v>
+        <v>133236969</v>
       </c>
       <c r="B13" t="n">
-        <v>81318</v>
+        <v>57145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448126</v>
+        <v>448047</v>
       </c>
       <c r="R13" t="n">
-        <v>6803611</v>
+        <v>6803686</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,7 +1958,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1963,7 +1968,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1990,50 +1995,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133236969</v>
+        <v>133236978</v>
       </c>
       <c r="B14" t="n">
-        <v>57145</v>
+        <v>81318</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448047</v>
+        <v>448126</v>
       </c>
       <c r="R14" t="n">
-        <v>6803686</v>
+        <v>6803611</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 62355-2022 artfynd.xlsx
+++ b/artfynd/A 62355-2022 artfynd.xlsx
@@ -786,45 +786,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133236983</v>
+        <v>133236990</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448089</v>
+        <v>448080</v>
       </c>
       <c r="R3" t="n">
-        <v>6803668</v>
+        <v>6803714</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,38 +898,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133236990</v>
+        <v>133236975</v>
       </c>
       <c r="B4" t="n">
-        <v>57145</v>
+        <v>57958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448080</v>
+        <v>448125</v>
       </c>
       <c r="R4" t="n">
-        <v>6803714</v>
+        <v>6803620</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133236975</v>
+        <v>133236983</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,39 +1021,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448125</v>
+        <v>448089</v>
       </c>
       <c r="R5" t="n">
-        <v>6803620</v>
+        <v>6803668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1883,50 +1883,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133236969</v>
+        <v>133236978</v>
       </c>
       <c r="B13" t="n">
-        <v>57145</v>
+        <v>81318</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448047</v>
+        <v>448126</v>
       </c>
       <c r="R13" t="n">
-        <v>6803686</v>
+        <v>6803611</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,7 +1953,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1968,7 +1963,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1995,45 +1990,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133236978</v>
+        <v>133236969</v>
       </c>
       <c r="B14" t="n">
-        <v>81318</v>
+        <v>57145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkrok, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448126</v>
+        <v>448047</v>
       </c>
       <c r="R14" t="n">
-        <v>6803611</v>
+        <v>6803686</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 62355-2022 artfynd.xlsx
+++ b/artfynd/A 62355-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236978</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236988</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236989</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236964</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236983</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236975</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236969</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236990</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236993</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1766,6 +1816,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236972</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1882,6 +1937,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236973</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1993,6 +2053,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236982</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2104,6 +2169,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236987</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2215,6 +2285,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236994</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2322,8 +2397,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133236967</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>